--- a/output/pdf_financials_xlsx/MONA.P.xlsx
+++ b/output/pdf_financials_xlsx/MONA.P.xlsx
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.08788</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.057041</v>
       </c>
     </row>
     <row r="13">
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.047388</v>
+        <v>-0.040492</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.013033</v>
+        <v>-0.044008</v>
       </c>
     </row>
     <row r="28">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.047388</v>
+        <v>-0.040492</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.013033</v>
+        <v>-0.044008</v>
       </c>
     </row>
     <row r="30">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
